--- a/List.xlsx
+++ b/List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\win10\Dropbox\Claude Projects\Visual Studio\Telecom Department\Expense-Fuel Tracking\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Expense-Fuel Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB4D90E-D64C-43F5-8E2A-5F30A0F905BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54919E08-5D7A-4A33-98D9-8FCFD56A4A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Area</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>TRX</t>
+  </si>
+  <si>
+    <t>FTTS</t>
   </si>
 </sst>
 </file>
@@ -479,6 +482,9 @@
       <c r="B7" t="s">
         <v>12</v>
       </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
